--- a/rtss-mexico/src/main/resources/latinamerica/Latin-America-Population.xlsx
+++ b/rtss-mexico/src/main/resources/latinamerica/Latin-America-Population.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-mexico\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-mexico\src\main\resources\latinamerica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B199E647-ADC5-4152-B6B7-175CA9B9E15C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F562DCB-BC3F-406F-9017-3DEA0F47184C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="360" windowWidth="19125" windowHeight="23055" xr2:uid="{0C6DB7CF-7936-4F84-A18A-9F2841EE8776}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="2" xr2:uid="{0C6DB7CF-7936-4F84-A18A-9F2841EE8776}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="60">
   <si>
     <t>Statistical Abstract of Latin America (vol 38, 2002), UCLA Latin America Center Publications, стр. 150-159</t>
   </si>
@@ -212,6 +212,10 @@
   <si>
     <t>Statistical Abstract ofLatin America, Supplement 3 (1974) "Statistics and National Policy", UCLA Latin American Center, стр. 186</t>
   </si>
+  <si>
+    <t xml:space="preserve">Исправлена опечатка Парагвай 1966
+</t>
+  </si>
 </sst>
 </file>
 
@@ -255,7 +259,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -274,6 +278,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -287,7 +297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -324,6 +334,10 @@
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -717,6 +731,11 @@
         <v>29</v>
       </c>
     </row>
+    <row r="24" spans="1:2" ht="105" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>59</v>
+      </c>
+    </row>
     <row r="28" spans="1:2" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
         <v>41</v>
@@ -7748,7 +7767,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <f t="shared" ref="A4:A65" si="0">A3+1</f>
+        <f t="shared" ref="A4:A52" si="0">A3+1</f>
         <v>1902</v>
       </c>
       <c r="B4" s="7">
@@ -12023,8 +12042,8 @@
       <c r="Q68" s="7">
         <v>1272</v>
       </c>
-      <c r="R68" s="7">
-        <v>2961</v>
+      <c r="R68" s="17">
+        <v>2061</v>
       </c>
       <c r="S68" s="7">
         <v>12012</v>

--- a/rtss-mexico/src/main/resources/latinamerica/Latin-America-Population.xlsx
+++ b/rtss-mexico/src/main/resources/latinamerica/Latin-America-Population.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-mexico\src\main\resources\latinamerica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F562DCB-BC3F-406F-9017-3DEA0F47184C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0F97F5-E820-4AC8-9ED3-D61320123D68}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" activeTab="2" xr2:uid="{0C6DB7CF-7936-4F84-A18A-9F2841EE8776}"/>
+    <workbookView xWindow="4950" yWindow="1725" windowWidth="26805" windowHeight="22275" xr2:uid="{0C6DB7CF-7936-4F84-A18A-9F2841EE8776}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -213,8 +213,7 @@
     <t>Statistical Abstract ofLatin America, Supplement 3 (1974) "Statistics and National Policy", UCLA Latin American Center, стр. 186</t>
   </si>
   <si>
-    <t xml:space="preserve">Исправлена опечатка Парагвай 1966
-</t>
+    <t>Исправлена опечатка Парагвай 1966</t>
   </si>
 </sst>
 </file>
@@ -297,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -336,9 +335,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -653,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3493652F-D782-4B7C-88EB-67D8DCBAAE8F}">
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" ht="23.25" x14ac:dyDescent="0.35">
@@ -731,43 +727,43 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="105" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A28" s="12" t="s">
+    <row r="27" spans="1:2" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A27" s="12" t="s">
         <v>41</v>
       </c>
     </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+    </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="A29" s="1" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
         <v>44</v>
       </c>
     </row>
